--- a/test_samples/YJE_TATA/sample4_ref.xlsx
+++ b/test_samples/YJE_TATA/sample4_ref.xlsx
@@ -15,7 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="新細明體"/>
@@ -64,12 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -435,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="4"/>
@@ -539,6 +542,17 @@
 貨櫃號碼</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Shipper
+出貨方</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -606,7 +620,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7PKG/117KG</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -617,6 +631,16 @@
       <c r="P2" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>TAY NINH KUO YUEN LTD</t>
         </is>
       </c>
     </row>
@@ -686,7 +710,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7PKG/117KG</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -697,6 +721,16 @@
       <c r="P3" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>TAY NINH KUO YUEN LTD</t>
         </is>
       </c>
     </row>
@@ -766,7 +800,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7PKG/117KG</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -777,6 +811,16 @@
       <c r="P4" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>TAY NINH KUO YUEN LTD</t>
         </is>
       </c>
     </row>
@@ -846,7 +890,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7PKG/117KG</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -857,6 +901,16 @@
       <c r="P5" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>TAY NINH KUO YUEN LTD</t>
         </is>
       </c>
     </row>
@@ -926,7 +980,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7PKG/117KG</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -937,6 +991,16 @@
       <c r="P6" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>TAY NINH KUO YUEN LTD</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1070,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7PKG/117KG</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1017,6 +1081,104 @@
       <c r="P7" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>TAY NINH KUO YUEN LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>45660</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TH20250065</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PT TATA HARMONI SARANATAMA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PT GLOSTAR INDONESIA (CJR)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PPN 12%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>A2412195-S</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>978-22039334</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>7PKG/117KG</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>VJ855</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>332118</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>TAY NINH KUO YUEN LTD</t>
         </is>
       </c>
     </row>
